--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.50141395213565</v>
+        <v>7.556479767222044</v>
       </c>
       <c r="D2" t="n">
-        <v>45.26326934282167</v>
+        <v>7.355281268208521</v>
       </c>
       <c r="E2" t="n">
-        <v>16.60343493946575</v>
+        <v>2.698058177663184</v>
       </c>
       <c r="F2" t="n">
-        <v>15.27935045033259</v>
+        <v>2.482894448179046</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.65926125520597</v>
+        <v>9.694629953970971</v>
       </c>
       <c r="D3" t="n">
-        <v>8.461970117626544</v>
+        <v>1.375070144114313</v>
       </c>
       <c r="E3" t="n">
-        <v>16.60343493946575</v>
+        <v>2.698058177663184</v>
       </c>
       <c r="F3" t="n">
-        <v>15.27935045033259</v>
+        <v>2.482894448179046</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.86840631577662</v>
+        <v>8.2661160263137</v>
       </c>
       <c r="D4" t="n">
-        <v>49.67513086001419</v>
+        <v>8.072208764752306</v>
       </c>
       <c r="E4" t="n">
-        <v>16.60343493946575</v>
+        <v>2.698058177663184</v>
       </c>
       <c r="F4" t="n">
-        <v>15.27935045033259</v>
+        <v>2.482894448179046</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.14586893970406</v>
+        <v>4.24870370270191</v>
       </c>
       <c r="D5" t="n">
-        <v>25.13317927773779</v>
+        <v>4.084141632632391</v>
       </c>
       <c r="E5" t="n">
-        <v>16.60343493946575</v>
+        <v>2.698058177663184</v>
       </c>
       <c r="F5" t="n">
-        <v>15.27935045033259</v>
+        <v>2.482894448179046</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.830486364150696</v>
+        <v>1.597454034174488</v>
       </c>
       <c r="D6" t="n">
-        <v>10.96683799088493</v>
+        <v>1.782111173518801</v>
       </c>
       <c r="E6" t="n">
-        <v>16.60343493946575</v>
+        <v>2.698058177663184</v>
       </c>
       <c r="F6" t="n">
-        <v>15.27935045033259</v>
+        <v>2.482894448179046</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.076538535293224</v>
+        <v>1.312437511985149</v>
       </c>
       <c r="D7" t="n">
-        <v>6.431925155116339</v>
+        <v>1.045187837706405</v>
       </c>
       <c r="E7" t="n">
-        <v>16.60343493946575</v>
+        <v>2.698058177663184</v>
       </c>
       <c r="F7" t="n">
-        <v>15.27935045033259</v>
+        <v>2.482894448179046</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.35729208461035</v>
+        <v>4.608059963749182</v>
       </c>
       <c r="D8" t="n">
-        <v>8.496687427293015</v>
+        <v>1.380711706935115</v>
       </c>
       <c r="E8" t="n">
-        <v>16.60343493946575</v>
+        <v>2.698058177663184</v>
       </c>
       <c r="F8" t="n">
-        <v>15.27935045033259</v>
+        <v>2.482894448179046</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.51682984641085</v>
+        <v>4.796484850041764</v>
       </c>
       <c r="D9" t="n">
-        <v>29.24695448381636</v>
+        <v>4.752630103620159</v>
       </c>
       <c r="E9" t="n">
-        <v>16.60343493946575</v>
+        <v>2.698058177663184</v>
       </c>
       <c r="F9" t="n">
-        <v>15.27935045033259</v>
+        <v>2.482894448179046</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.24971119363453</v>
+        <v>4.265578068965612</v>
       </c>
       <c r="D10" t="n">
-        <v>26.20291865090004</v>
+        <v>4.257974280771257</v>
       </c>
       <c r="E10" t="n">
-        <v>16.60343493946575</v>
+        <v>2.698058177663184</v>
       </c>
       <c r="F10" t="n">
-        <v>15.27935045033259</v>
+        <v>2.482894448179046</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
